--- a/data/dataset/tables/ножи.xlsx
+++ b/data/dataset/tables/ножи.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15600" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ножи" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ножи" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ножи'!$A$1:$I$262</definedName>
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I262"/>
+  <dimension ref="A1:H262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23.7109375" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -493,17 +493,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,17 +533,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -573,17 +573,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -613,17 +613,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -653,17 +653,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>петельчатая рукоять</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>петельчатая рукоять</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Железо, латунь, медь, алюминий, свинец, пластмасса</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -789,11 +789,6 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>не указано</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>не нужно</t>
         </is>
       </c>
     </row>
@@ -813,12 +808,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Железо, латунь, медь, алюминий, свинец, пластмасса</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -834,11 +829,6 @@
       <c r="H10" t="inlineStr">
         <is>
           <t>не указано</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>не нужно</t>
         </is>
       </c>
     </row>
@@ -858,12 +848,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Железо, латунь, медь, алюминий, свинец, пластмасса</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -879,11 +869,6 @@
       <c r="H11" t="inlineStr">
         <is>
           <t>не указано</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>не нужно</t>
         </is>
       </c>
     </row>
@@ -903,12 +888,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Железо, латунь, медь, алюминий, свинец, пластмасса</t>
+          <t>не указано</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -924,11 +909,6 @@
       <c r="H12" t="inlineStr">
         <is>
           <t>не указано</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>не нужно</t>
         </is>
       </c>
     </row>
@@ -953,17 +933,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>коленчатый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>грибовидное окончание</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -993,17 +973,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>коленчатый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>грибовидное окончание</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1033,17 +1013,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>коленчатый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>грибовидное окончание</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1073,17 +1053,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>коленчатый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>грибовидное окончание</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1113,17 +1093,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1153,17 +1133,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1193,17 +1173,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1233,17 +1213,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1273,17 +1253,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1313,17 +1293,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1353,17 +1333,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1393,17 +1373,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1433,17 +1413,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1473,17 +1453,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1513,17 +1493,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1553,17 +1533,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1593,17 +1573,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1633,17 +1613,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1673,17 +1653,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1713,17 +1693,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1753,17 +1733,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1793,17 +1773,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1833,17 +1813,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1868,12 +1848,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1908,12 +1888,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1948,12 +1928,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1988,12 +1968,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2028,12 +2008,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2043,7 +2023,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2068,12 +2048,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2083,7 +2063,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2108,12 +2088,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2123,7 +2103,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2148,12 +2128,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2163,7 +2143,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2188,12 +2168,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2203,7 +2183,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2228,12 +2208,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2243,7 +2223,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2268,12 +2248,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2283,7 +2263,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2308,12 +2288,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2323,7 +2303,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2348,12 +2328,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2363,7 +2343,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2388,12 +2368,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2403,7 +2383,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2428,22 +2408,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2468,22 +2448,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2508,22 +2488,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2548,22 +2528,22 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2588,22 +2568,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2628,22 +2608,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2668,12 +2648,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2683,7 +2663,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2708,22 +2688,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2748,22 +2728,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2788,22 +2768,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>коленчатый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2828,22 +2808,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>коленчатый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2868,22 +2848,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>коленчатый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2908,22 +2888,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2948,22 +2928,22 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2988,22 +2968,22 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3028,12 +3008,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3043,7 +3023,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3068,12 +3048,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3083,7 +3063,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3108,22 +3088,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3148,22 +3128,22 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3188,22 +3168,22 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3228,12 +3208,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3243,7 +3223,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3268,12 +3248,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3283,7 +3263,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3308,12 +3288,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3323,7 +3303,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3348,12 +3328,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3363,7 +3343,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3388,12 +3368,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3403,7 +3383,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3428,12 +3408,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3468,12 +3448,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3508,12 +3488,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3548,22 +3528,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -3588,22 +3568,22 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3628,22 +3608,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3668,22 +3648,22 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3708,22 +3688,22 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3748,22 +3728,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -3788,22 +3768,22 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3828,22 +3808,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3868,22 +3848,22 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -3913,17 +3893,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3953,17 +3933,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -3993,17 +3973,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4033,17 +4013,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4073,17 +4053,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4113,7 +4093,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4123,7 +4103,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4153,7 +4133,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4163,7 +4143,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4193,7 +4173,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4203,7 +4183,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4233,7 +4213,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4273,7 +4253,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4313,7 +4293,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4353,17 +4333,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4393,17 +4373,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4428,22 +4408,22 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4468,22 +4448,22 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4508,22 +4488,22 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -4548,22 +4528,22 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4588,22 +4568,22 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4628,22 +4608,22 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4668,22 +4648,22 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4708,22 +4688,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4748,22 +4728,22 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4788,22 +4768,22 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -4828,22 +4808,22 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -4868,22 +4848,22 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -4908,22 +4888,22 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4948,22 +4928,22 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4988,22 +4968,22 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5028,22 +5008,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5068,22 +5048,22 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5108,22 +5088,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5148,22 +5128,22 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5188,22 +5168,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5228,22 +5208,22 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5268,22 +5248,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5308,22 +5288,22 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -5348,22 +5328,22 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -5388,22 +5368,22 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5428,12 +5408,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5443,7 +5423,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -5468,12 +5448,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -5483,7 +5463,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -5508,22 +5488,22 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5548,22 +5528,22 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5588,22 +5568,22 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5628,22 +5608,22 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5668,22 +5648,22 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5708,22 +5688,22 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5748,22 +5728,22 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5788,22 +5768,22 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -5828,22 +5808,22 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5868,22 +5848,22 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>листовидный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -5908,22 +5888,22 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>листовидный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -5948,22 +5928,22 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>листовидный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -5988,22 +5968,22 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -6028,22 +6008,22 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -6068,22 +6048,22 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -6108,22 +6088,22 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -6148,22 +6128,22 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -6188,22 +6168,22 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -6228,22 +6208,22 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6268,22 +6248,22 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -6308,22 +6288,22 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>змейчатообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -6348,22 +6328,22 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>змейчатообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -6388,22 +6368,22 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>змейчатообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -6428,22 +6408,22 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -6468,22 +6448,22 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -6508,12 +6488,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -6523,7 +6503,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6548,12 +6528,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -6563,7 +6543,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -6588,12 +6568,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6603,7 +6583,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -6628,12 +6608,12 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -6643,7 +6623,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -6668,22 +6648,22 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>петельчатая рукоять</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6708,22 +6688,22 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>петельчатая рукоять</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -6748,22 +6728,22 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>петельчатая рукоять</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -6788,22 +6768,22 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>петельчатая рукоять</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6828,22 +6808,22 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>петельчатая рукоять</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -6868,22 +6848,22 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6908,22 +6888,22 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -6948,22 +6928,22 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6988,12 +6968,12 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -7003,7 +6983,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -7028,12 +7008,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -7043,7 +7023,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -7068,12 +7048,12 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -7083,7 +7063,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -7108,22 +7088,22 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -7148,22 +7128,22 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -7188,22 +7168,22 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -7228,22 +7208,22 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -7268,22 +7248,22 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -7308,22 +7288,22 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -7348,22 +7328,22 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -7388,22 +7368,22 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -7428,22 +7408,22 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -7468,22 +7448,22 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -7508,22 +7488,22 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -7548,22 +7528,22 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>змейчатообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -7588,22 +7568,22 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>змейчатообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -7628,22 +7608,22 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>змейчатообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -7668,22 +7648,22 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -7708,22 +7688,22 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -7748,22 +7728,22 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -7788,22 +7768,22 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -7828,22 +7808,22 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -7868,22 +7848,22 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -7908,22 +7888,22 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -7948,22 +7928,22 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -7988,22 +7968,22 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -8028,22 +8008,22 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -8068,22 +8048,22 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -8108,22 +8088,22 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -8148,22 +8128,22 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -8188,22 +8168,22 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -8228,22 +8208,22 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -8268,22 +8248,22 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -8308,22 +8288,22 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -8348,22 +8328,22 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -8388,22 +8368,22 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -8428,22 +8408,22 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -8468,22 +8448,22 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -8508,22 +8488,22 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -8548,22 +8528,22 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -8588,22 +8568,22 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -8628,22 +8608,22 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -8668,22 +8648,22 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -8708,22 +8688,22 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -8748,22 +8728,22 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>змейчатообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -8788,22 +8768,22 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>змейчатообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -8828,22 +8808,22 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>змейчатообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -8868,22 +8848,22 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>змейчатообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -8908,22 +8888,22 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -8948,22 +8928,22 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -8988,22 +8968,22 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -9028,22 +9008,22 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -9068,22 +9048,22 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -9108,22 +9088,22 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -9148,22 +9128,22 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -9188,22 +9168,22 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -9228,22 +9208,22 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -9268,22 +9248,22 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -9308,22 +9288,22 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -9348,22 +9328,22 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -9388,22 +9368,22 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -9428,22 +9408,22 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -9468,22 +9448,22 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -9508,22 +9488,22 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -9548,22 +9528,22 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -9588,22 +9568,22 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -9628,22 +9608,22 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>змейчатообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -9668,22 +9648,22 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>змейчатообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -9708,22 +9688,22 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>змейчатообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -9748,22 +9728,22 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>змейчатообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -9788,22 +9768,22 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Целый и фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>змейчатообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -9828,22 +9808,22 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -9868,22 +9848,22 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -9908,22 +9888,22 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -9948,22 +9928,22 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -9988,22 +9968,22 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>без выделенной рукояти</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -10028,17 +10008,17 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -10068,17 +10048,17 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -10108,17 +10088,17 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -10148,22 +10128,22 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -10188,22 +10168,22 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -10228,22 +10208,22 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -10268,17 +10248,17 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -10308,17 +10288,17 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -10348,22 +10328,22 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -10388,22 +10368,22 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -10428,12 +10408,12 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -10443,7 +10423,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -10468,12 +10448,12 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -10483,7 +10463,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -10508,12 +10488,12 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -10523,7 +10503,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -10548,22 +10528,22 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -10588,22 +10568,22 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -10628,22 +10608,22 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>выпуклообушковый</t>
+          <t>изогнутый</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -10668,12 +10648,12 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -10689,11 +10669,6 @@
       <c r="H256" t="inlineStr">
         <is>
           <t>не указано</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>не нужно</t>
         </is>
       </c>
     </row>
@@ -10713,12 +10688,12 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -10734,11 +10709,6 @@
       <c r="H257" t="inlineStr">
         <is>
           <t>не указано</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>не нужно</t>
         </is>
       </c>
     </row>
@@ -10758,12 +10728,12 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -10779,11 +10749,6 @@
       <c r="H258" t="inlineStr">
         <is>
           <t>не указано</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>не нужно</t>
         </is>
       </c>
     </row>
@@ -10803,12 +10768,12 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -10818,7 +10783,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -10843,12 +10808,12 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Фрагмент</t>
+          <t>сломан</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -10858,7 +10823,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>есть</t>
+          <t>выделенная</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -10883,22 +10848,22 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -10923,22 +10888,22 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Бронза</t>
+          <t>бронза</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Целый</t>
+          <t>целый</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>прямолезвийный</t>
+          <t>прямой</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>нет</t>
+          <t>невыделенная</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
